--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N218_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N218_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.26065213892831</v>
+        <v>15.80485597257585</v>
       </c>
       <c r="D2" t="n">
-        <v>10.16093583427584</v>
+        <v>1.651152073069824</v>
       </c>
       <c r="E2" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F2" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.32528218513204</v>
+        <v>10.29035835508396</v>
       </c>
       <c r="D3" t="n">
-        <v>60.0210902256106</v>
+        <v>9.753427161661723</v>
       </c>
       <c r="E3" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F3" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.760928282235143</v>
+        <v>0.6111508458632107</v>
       </c>
       <c r="D4" t="n">
-        <v>10.19889830096037</v>
+        <v>1.657320973906061</v>
       </c>
       <c r="E4" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F4" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.54515743496253</v>
+        <v>9.351088083181413</v>
       </c>
       <c r="D5" t="n">
-        <v>37.20102796373522</v>
+        <v>6.045167044106973</v>
       </c>
       <c r="E5" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F5" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.68176818349372</v>
+        <v>6.44828732981773</v>
       </c>
       <c r="D6" t="n">
-        <v>36.67640649118337</v>
+        <v>5.959916054817298</v>
       </c>
       <c r="E6" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F6" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.72023256018647</v>
+        <v>9.054537791030301</v>
       </c>
       <c r="D7" t="n">
-        <v>17.32963982607455</v>
+        <v>2.816066471737114</v>
       </c>
       <c r="E7" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F7" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.73089190412683</v>
+        <v>7.43126993442061</v>
       </c>
       <c r="D8" t="n">
-        <v>22.28036640527235</v>
+        <v>3.620559540856756</v>
       </c>
       <c r="E8" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F8" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.67866348606336</v>
+        <v>7.585282816485296</v>
       </c>
       <c r="D9" t="n">
-        <v>23.08053095148927</v>
+        <v>3.750586279617006</v>
       </c>
       <c r="E9" t="n">
-        <v>24.39976215217241</v>
+        <v>3.964961349728017</v>
       </c>
       <c r="F9" t="n">
-        <v>15.75181659523127</v>
+        <v>2.559670196725081</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
